--- a/mapping/templates/GUIDE_Doppio/API_CRS620MI_Supplier.xlsx
+++ b/mapping/templates/GUIDE_Doppio/API_CRS620MI_Supplier.xlsx
@@ -162,170 +162,10 @@
     <author>System</author>
   </authors>
   <commentList>
-    <comment ref="B1" authorId="0" shapeId="0">
-      <text>
-        <t xml:space="preserve">Supplier
-The field indicates the unique identity of a supplier.
-</t>
-      </text>
-    </comment>
-    <comment ref="C1" authorId="0" shapeId="0">
-      <text>
-        <t>Address type
-The field indicates the type of address to use.
-01: Postal address
-02: Street address
-03: Pickup address
-04: Origin address
-05: Final delivery address
-10: Bank address</t>
-      </text>
-    </comment>
-    <comment ref="D1" authorId="0" shapeId="0">
-      <text>
-        <t xml:space="preserve">Address number
-The field indicates address number and is used to identify a record in the address file.
-The address may contain up to 6 alphanumeric characters.
-</t>
-      </text>
-    </comment>
-    <comment ref="E1" authorId="0" shapeId="0">
-      <text>
-        <t xml:space="preserve">Start date
-The field indicates the date from when the service is valid. The start date can be left blank if there is no date specified for when the service should become valid.
-For scheduled services, the start date can be used to define the date of the first scheduled service. The start date in (MOS300) has no impact on scheduled services if a record exists in (MMS242).
-</t>
-      </text>
-    </comment>
-    <comment ref="F1" authorId="0" shapeId="0">
-      <text>
-        <t xml:space="preserve">Supplier name
-The field indicates supplier name, most often the supplier's company name.
-</t>
-      </text>
-    </comment>
-    <comment ref="G1" authorId="0" shapeId="0">
-      <text>
-        <t xml:space="preserve">Address line 1
-The field indicates an address line. A maximum of 36 characters may be used.
-</t>
-      </text>
-    </comment>
-    <comment ref="H1" authorId="0" shapeId="0">
-      <text>
-        <t xml:space="preserve">Address line 3
-The field indicates an address line. It can contain a maximum of 36 positions.
-</t>
-      </text>
-    </comment>
-    <comment ref="I1" authorId="0" shapeId="0">
-      <text>
-        <t xml:space="preserve">Address line 4
-The field indicates an address line. It can contain a maximum of 36 positions.
-</t>
-      </text>
-    </comment>
-    <comment ref="J1" authorId="0" shapeId="0">
-      <text>
-        <t xml:space="preserve">City
-The field indicates the city in an address. The information is mandatory when address formatting is used, and when a city is an address element used in the formatting rule (CRS117). Address formatting rules are defined for each country (CRS045).
-</t>
-      </text>
-    </comment>
-    <comment ref="K1" authorId="0" shapeId="0">
-      <text>
-        <t xml:space="preserve">State
-The field indicates an area, province or state within a country. The information is used for addresses, U.S. sales tax and for trade statistics.
-When editing addresses, the information is validated when state is used as an address element according to the address formatting rule (CRS117), used for the country to which the address applies. Address formatting rules are stated for each country (CRS045/E).
-</t>
-      </text>
-    </comment>
-    <comment ref="L1" authorId="0" shapeId="0">
-      <text>
-        <t xml:space="preserve">Postal code
-The field indicates a postal code for a specific address.
-The postal code is an address element that can be part of an address line if address formatting rules in (CRS117) are used.
-Select 'Validate Postal' in (CRS045) to activate validation of the postal code against (CRS044).
-</t>
-      </text>
-    </comment>
-    <comment ref="M1" authorId="0" shapeId="0">
-      <text>
-        <t xml:space="preserve">Country
-The field indicates the country from which goods were sent. Depending on settings, it can in fact also be the recipient of the invoice connected to this transaction.
-The country code can be retrieved from a customer, customer delivery address, fiscal representative, supplier or warehouse. It can also be retrieved from an internal supplier or a customer, depending on settings and scenarios.
-The rule of thumb is that the same rule applies to the country code as when retrieving the VAT registration number. However, the country code in the VAT registration number will not be identical to this field.
-</t>
-      </text>
-    </comment>
-  </commentList>
-</comments>
-</file>
-
-<file path=xl/comments/comment2.xml><?xml version="1.0" encoding="utf-8"?>
-<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <authors>
-    <author>System</author>
-  </authors>
-  <commentList>
-    <comment ref="B1" authorId="0" shapeId="0">
-      <text>
-        <t xml:space="preserve">Supplier
-The field indicates the unique identity of a supplier.
-</t>
-      </text>
-    </comment>
     <comment ref="C1" authorId="0" shapeId="0">
       <text>
         <t xml:space="preserve">Supplier
 The field indicates the unique identity of a supplier.
-</t>
-      </text>
-    </comment>
-    <comment ref="D1" authorId="0" shapeId="0">
-      <text>
-        <t xml:space="preserve">Supplier name
-The field indicates supplier name, most often the supplier's company name.
-</t>
-      </text>
-    </comment>
-    <comment ref="E1" authorId="0" shapeId="0">
-      <text>
-        <t>Supplier type
-The field indicates a supplier type.
-0: Supplier
-1: Agent
-2: Only payee
-3: Supplier group
-5: Forwarding agent
-6: Insurance company
-7: Supplier for internal sales
-8: Miscellaneous suppliers
-9: Trade-in supplier</t>
-      </text>
-    </comment>
-    <comment ref="F1" authorId="0" shapeId="0">
-      <text>
-        <t xml:space="preserve">Search key
-The field indicates a search key.
-The ten-character search key for searching in the customer and supplier files can be an abbreviation of the customer and supplier names.
-If the search key is not entered when creating a new customer or supplier in (CRS610) and (CRS620) respectively, the first ten characters of the name are used for the search key field.
-</t>
-      </text>
-    </comment>
-    <comment ref="G1" authorId="0" shapeId="0">
-      <text>
-        <t xml:space="preserve">Country
-The field indicates the country from which goods were sent. Depending on settings, it can in fact also be the recipient of the invoice connected to this transaction.
-The country code can be retrieved from a customer, customer delivery address, fiscal representative, supplier or warehouse. It can also be retrieved from an internal supplier or a customer, depending on settings and scenarios.
-The rule of thumb is that the same rule applies to the country code as when retrieving the VAT registration number. However, the country code in the VAT registration number will not be identical to this field.
-</t>
-      </text>
-    </comment>
-    <comment ref="H1" authorId="0" shapeId="0">
-      <text>
-        <t xml:space="preserve">Language
-The field indicates the language in which external documents are to be printed. Note that invoices in the order system are printed in the language indicated in (CRS610) for the invoice recipient.
 </t>
       </text>
     </comment>
@@ -409,13 +249,11 @@
     </comment>
     <comment ref="R1" authorId="0" shapeId="0">
       <text>
-        <t xml:space="preserve">Exchange rate type
-The field indicates the exchange rate used when prices in the Purchase module are converted to local currency or another currency.
-In the following functions, the exchange rate type is retrieved as described below:
-In other functions, the exchange rate type specified in (CRS780) is used.
-If an agreement reference exists, the agreement's exchange rate type is used. If there is no agreement reference, the type specified for the supplier is used.
-When a new supplier is entered, a default exchange rate type is proposed from (CRS780). When an agreement is entered, the exchange rate type is proposed from (CRS624).
-</t>
+        <t>Exchange rate type
+The field indicates the exchange rate type, such as variable rate, budget exchange rate, or rate used for group consolidation.
+Exchange rate types are used for budgeting and annual financial statements and can be connected to customers, suppliers, and price lists.
+01: Variable rate
+02-99: User-defined.</t>
       </text>
     </comment>
     <comment ref="S1" authorId="0" shapeId="0">
@@ -440,14 +278,6 @@
 The field indicates which rule should be used when calculating attribute-based prices or charges.
 1: Expected attribute values are used as base
 2: Actual attribute values are used as base.</t>
-      </text>
-    </comment>
-    <comment ref="V1" authorId="0" shapeId="0">
-      <text>
-        <t xml:space="preserve">Alternate lang for option description
-The field indicates the language code to use when printing the option description from a product configuration. If no code is entered, the language code from the customer/supplier is used.
-The option description is used in all cases where the options are identical, but customers with the same language must have different option descriptions.
-</t>
       </text>
     </comment>
     <comment ref="W1" authorId="0" shapeId="0">
@@ -1171,7 +1001,6 @@
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-  <legacyDrawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="anysvml"/>
 </worksheet>
 </file>
 
